--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.78644028787171</v>
+        <v>4.190296546779153</v>
       </c>
       <c r="D2" t="n">
-        <v>27.33769224228865</v>
+        <v>4.442374989371906</v>
       </c>
       <c r="E2" t="n">
-        <v>8.910742101956377</v>
+        <v>1.447995591567911</v>
       </c>
       <c r="F2" t="n">
-        <v>6.381982066812023</v>
+        <v>1.037072085856954</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.92262576060478</v>
+        <v>5.837426686098278</v>
       </c>
       <c r="D3" t="n">
-        <v>31.66228039797513</v>
+        <v>5.145120564670958</v>
       </c>
       <c r="E3" t="n">
-        <v>8.910742101956377</v>
+        <v>1.447995591567911</v>
       </c>
       <c r="F3" t="n">
-        <v>6.381982066812023</v>
+        <v>1.037072085856954</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.7455617108585</v>
+        <v>6.783653778014507</v>
       </c>
       <c r="D4" t="n">
-        <v>14.34017516833642</v>
+        <v>2.330278464854669</v>
       </c>
       <c r="E4" t="n">
-        <v>8.910742101956377</v>
+        <v>1.447995591567911</v>
       </c>
       <c r="F4" t="n">
-        <v>6.381982066812023</v>
+        <v>1.037072085856954</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.28183064851424</v>
+        <v>8.170797480383564</v>
       </c>
       <c r="D5" t="n">
-        <v>23.75920874103344</v>
+        <v>3.860871420417935</v>
       </c>
       <c r="E5" t="n">
-        <v>8.910742101956377</v>
+        <v>1.447995591567911</v>
       </c>
       <c r="F5" t="n">
-        <v>6.381982066812023</v>
+        <v>1.037072085856954</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
